--- a/docs/Datos.xlsx
+++ b/docs/Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNC\Documents\BANCO DE LA REP TERCERA MEDICIÓN 2026\SUBIRDATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8666239B-4119-4FD7-A96B-D06DC9329B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EC5A3A-ED57-4FC7-B2B6-C10FAD2579E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BA0F596D-090A-4821-9C40-CDFD8FF79E10}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="230">
   <si>
     <t>P1_1</t>
   </si>
@@ -717,6 +717,21 @@
   </si>
   <si>
     <t>3176488571  6044508888</t>
+  </si>
+  <si>
+    <t>EE027-1</t>
+  </si>
+  <si>
+    <t>CIA DE EMPAQUES S.A.</t>
+  </si>
+  <si>
+    <t>Vicepresidente Financiero</t>
+  </si>
+  <si>
+    <t>NATALIA.CADAVID@GRUPOEXCALA.COM; NOTIFICACIONES@GRUPOEXCALA.COM</t>
+  </si>
+  <si>
+    <t>3658881</t>
   </si>
 </sst>
 </file>
@@ -791,7 +806,37 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{83731630-F151-46BF-8E82-D67ECD727456}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1142,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71CCDC68-D418-44C9-BA59-ABBE0301C86C}">
-  <dimension ref="A1:BI25"/>
+  <dimension ref="A1:BI26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
@@ -5723,11 +5768,195 @@
         <v>50</v>
       </c>
     </row>
+    <row r="26" spans="1:61" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="G26" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="H26" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="K26" s="2">
+        <v>4</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M26" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>3200</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>3300</v>
+      </c>
+      <c r="R26" s="2">
+        <v>3400</v>
+      </c>
+      <c r="S26" s="2">
+        <v>3400</v>
+      </c>
+      <c r="T26" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="U26" s="2">
+        <v>3</v>
+      </c>
+      <c r="V26" s="2">
+        <v>0</v>
+      </c>
+      <c r="W26" s="2">
+        <v>0</v>
+      </c>
+      <c r="X26" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>13</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="AB26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="2">
+        <v>2</v>
+      </c>
+      <c r="AD26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="2">
+        <v>2</v>
+      </c>
+      <c r="AJ26" s="2">
+        <v>2</v>
+      </c>
+      <c r="AK26" s="2">
+        <v>3</v>
+      </c>
+      <c r="AL26" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM26" s="2">
+        <v>2</v>
+      </c>
+      <c r="AN26" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO26" s="2">
+        <v>6</v>
+      </c>
+      <c r="AP26" s="2">
+        <v>5</v>
+      </c>
+      <c r="AQ26" s="2">
+        <v>8</v>
+      </c>
+      <c r="AR26" s="2">
+        <v>7</v>
+      </c>
+      <c r="AS26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AT26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AX26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ26" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA26" s="2">
+        <v>3</v>
+      </c>
+      <c r="BB26" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="BC26" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BD26" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="BE26" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="BF26" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="BG26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH26" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:BI1" xr:uid="{71CCDC68-D418-44C9-BA59-ABBE0301C86C}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
